--- a/results/Int All Data 0.1/Rando_9_permute.xlsx
+++ b/results/Int All Data 0.1/Rando_9_permute.xlsx
@@ -440,217 +440,217 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.853505171386798</v>
+        <v>0.8522794714896843</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8547636324254075</v>
+        <v>0.8522794714896843</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8552233714192885</v>
+        <v>0.853477554556777</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8534680781935344</v>
+        <v>0.8555114528618617</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8537466832728651</v>
+        <v>0.8557900579411923</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8593886391942384</v>
+        <v>0.8564680240428872</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8575125900254508</v>
+        <v>0.8549542427032003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8582509340986625</v>
+        <v>0.8592497427844263</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8565931120376888</v>
+        <v>0.8577730546380029</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8539183408241728</v>
+        <v>0.868499756322088</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8534586018302919</v>
+        <v>0.8597974765798451</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8510391509178534</v>
+        <v>0.8627275680944387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8541132831537337</v>
+        <v>0.8650400714788542</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8545730221476147</v>
+        <v>0.8659733578816267</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8553113662208263</v>
+        <v>0.8666513239833216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8576842475767585</v>
+        <v>0.8725442681540044</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8576842475767585</v>
+        <v>0.8762221801050523</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8585433475930038</v>
+        <v>0.8760410461905019</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8659267883251205</v>
+        <v>0.8760410461905019</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.868021064601722</v>
+        <v>0.8800484648291547</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8640878323495966</v>
+        <v>0.8728927275680944</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8640878323495966</v>
+        <v>0.8684255699355607</v>
       </c>
     </row>
     <row r="24">
@@ -660,1273 +660,1273 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8596577679103266</v>
+        <v>0.8676872258623491</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8596577679103266</v>
+        <v>0.8732411869821844</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8601175069042075</v>
+        <v>0.8739191530838794</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.859160935723182</v>
+        <v>0.8728418259598202</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8609998916987058</v>
+        <v>0.8735197920615151</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8621375967942817</v>
+        <v>0.8728418259598202</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8621375967942817</v>
+        <v>0.8718852547787946</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8617382357719174</v>
+        <v>0.8711469107055829</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8577213407700222</v>
+        <v>0.8696702225591595</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8584596848432339</v>
+        <v>0.8693312395083121</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8584596848432339</v>
+        <v>0.8715833649212108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8541641847620078</v>
+        <v>0.8719223479720583</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8589565170303786</v>
+        <v>0.8742348513564737</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8589565170303786</v>
+        <v>0.8724286565224455</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8567414848107435</v>
+        <v>0.8739053446688687</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8582181729571668</v>
+        <v>0.8779127633075214</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8593929712460064</v>
+        <v>0.8795473005902421</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8593929712460064</v>
+        <v>0.8808428548221151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8588728542806087</v>
+        <v>0.8810007039584122</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8516101694915255</v>
+        <v>0.8807220988790816</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8492001949423296</v>
+        <v>0.8834339632858612</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8488008339199653</v>
+        <v>0.8847898954892511</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8502404288731251</v>
+        <v>0.8845112904099204</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8529755780581578</v>
+        <v>0.8835547192288948</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8514988899117344</v>
+        <v>0.8810610819299292</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8537743001028862</v>
+        <v>0.8764360751610982</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8503008068446418</v>
+        <v>0.8740028158336492</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8503008068446418</v>
+        <v>0.8720154870850707</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8510995288893702</v>
+        <v>0.8770165700980127</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8495529864081875</v>
+        <v>0.8736638327828017</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.850593220338983</v>
+        <v>0.8732877565386907</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8504353712026859</v>
+        <v>0.8723915633291818</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8479046407104565</v>
+        <v>0.8640282666377863</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8479046407104565</v>
+        <v>0.8666892294362918</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.851861157740835</v>
+        <v>0.8576013970866951</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8523907510694753</v>
+        <v>0.8570355228244977</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8538441544376456</v>
+        <v>0.8554518871500515</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8558409595494667</v>
+        <v>0.8597982888395517</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8546428764823739</v>
+        <v>0.8454868143174311</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8546428764823739</v>
+        <v>0.8453289651811339</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8525856933990361</v>
+        <v>0.8430630313532246</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8525856933990361</v>
+        <v>0.8351784263821953</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8537837764661288</v>
+        <v>0.8320672009530514</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8521863323766719</v>
+        <v>0.8308087399144419</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8511090052526128</v>
+        <v>0.8152249959387015</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8524649374560026</v>
+        <v>0.8114590891861158</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.853263659500731</v>
+        <v>0.8124760383386581</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8519681052688579</v>
+        <v>0.8015543943250122</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8514014187469541</v>
+        <v>0.7580532842367467</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8510020577245898</v>
+        <v>0.774881680836086</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8490285373910218</v>
+        <v>0.7765162181188066</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8477096983808956</v>
+        <v>0.7765162181188066</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8458569339903612</v>
+        <v>0.7771941842205015</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8420444576812693</v>
+        <v>0.7777746791574158</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8413061136080575</v>
+        <v>0.7829758488113934</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8566258731791845</v>
+        <v>0.7927459793144528</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8614785834190719</v>
+        <v>0.7947798776195376</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8563472680998538</v>
+        <v>0.7927459793144528</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8563472680998538</v>
+        <v>0.7786760166783993</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8556089240266421</v>
+        <v>0.7779980505767043</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8556089240266421</v>
+        <v>0.7865933827909244</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8565284020144041</v>
+        <v>0.7865933827909244</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7154927708886121</v>
+        <v>0.7877310878865003</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7207586505658743</v>
+        <v>0.8030827963394163</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7018308333784589</v>
+        <v>0.8033381166404938</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7114715438349488</v>
+        <v>0.8033381166404938</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.727566740672551</v>
+        <v>0.8033381166404938</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7538038122055559</v>
+        <v>0.8013042183354091</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7483197054204798</v>
+        <v>0.7961168570964423</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7525220663886933</v>
+        <v>0.800124275735095</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.744860020577246</v>
+        <v>0.8011412248876375</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7429744950452157</v>
+        <v>0.8031751231927222</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7673682785509287</v>
+        <v>0.8031751231927222</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7598407970975254</v>
+        <v>0.8014802079384848</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7607602750852873</v>
+        <v>0.7916729842421617</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7607602750852873</v>
+        <v>0.7854272486056209</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7583321600693129</v>
+        <v>0.7535257486326962</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7595302431364055</v>
+        <v>0.7712270536632913</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7357686684355877</v>
+        <v>0.7696899875453511</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7421351600151622</v>
+        <v>0.7688170791140954</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7540788974928251</v>
+        <v>0.7524113283153734</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7570252342015487</v>
+        <v>0.7517566469919316</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7570252342015487</v>
+        <v>0.7480511182108627</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7511236259273298</v>
+        <v>0.7493001028862294</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7331196187794444</v>
+        <v>0.7492630096929658</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7062598148047869</v>
+        <v>0.7293510044945037</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.7085715059294959</v>
+        <v>0.7294113824660204</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.7076891211349976</v>
+        <v>0.7373753181350517</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6868110683922672</v>
+        <v>0.7373753181350517</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6864211837331456</v>
+        <v>0.7517152217468999</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6723046515405859</v>
+        <v>0.7513158607245356</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6717888666269562</v>
+        <v>0.7513158607245356</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6717888666269562</v>
+        <v>0.6779428169166621</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6766182920885904</v>
+        <v>0.6778220609736286</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.7296228407429468</v>
+        <v>0.6801345643580441</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.701269020414794</v>
+        <v>0.623012942004657</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.6671489684301727</v>
+        <v>0.6239091352141658</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6601786971354308</v>
+        <v>0.6246474792873775</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5884789083229545</v>
+        <v>0.628014025017599</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5788528185411815</v>
+        <v>0.628014025017599</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.575922727026588</v>
+        <v>0.6268056533275572</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5763824660204689</v>
+        <v>0.6164274110575622</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5773994151730113</v>
+        <v>0.5113442898142633</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5765868847132724</v>
+        <v>0.5116228948935939</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5781006660529594</v>
+        <v>0.5069978881247631</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5843973032977744</v>
+        <v>0.5069978881247631</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5843973032977744</v>
+        <v>0.5053633508420425</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5842765473547409</v>
+        <v>0.5050243677911951</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5753327557264309</v>
+        <v>0.5048432338766448</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.577000054150647</v>
+        <v>0.5048432338766448</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5894587642822331</v>
+        <v>0.5061387881085179</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.554761737152759</v>
+        <v>0.5060413169437374</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5485021931012076</v>
+        <v>0.5040677966101695</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5173157524232415</v>
+        <v>0.5040677966101695</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5089990252883522</v>
+        <v>0.5040677966101695</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5079078897492825</v>
+        <v>0.5036684355878053</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5056324795581307</v>
+        <v>0.5040074186386527</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5056324795581307</v>
+        <v>0.503947040667136</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5043973032977744</v>
+        <v>0.4994798830346023</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5079311745275357</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.4996006389776358</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.4996006389776358</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.4996006389776358</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.4996006389776358</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.4996006389776358</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.4996006389776358</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,27 +1946,27 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
